--- a/CE国試data/CE_questions_2022.xlsx
+++ b/CE国試data/CE_questions_2022.xlsx
@@ -3160,7 +3160,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T159" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T165" t="inlineStr">
